--- a/reports/集团总公司_利润表_2025-01.xlsx
+++ b/reports/集团总公司_利润表_2025-01.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>192421698</v>
+        <v>210328745</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>146216218</v>
+        <v>159234175</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>146216218</v>
+        <v>159234175</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>599753</v>
+        <v>772460</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>599753</v>
+        <v>772460</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>521017</v>
+        <v>677037</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>521017</v>
+        <v>677037</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>439404</v>
+        <v>572515</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>439404</v>
+        <v>572515</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>405369</v>
+        <v>529322</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>405369</v>
+        <v>529322</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>218986</v>
+        <v>291480</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>218986</v>
+        <v>291480</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>175823</v>
+        <v>229769</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>175823</v>
+        <v>229769</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>190061346</v>
+        <v>207256162</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>143855866</v>
+        <v>156161592</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>74057720</v>
+        <v>81749245</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>74057720</v>
+        <v>81749245</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1361350</v>
+        <v>2417365</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>1361350</v>
+        <v>2417365</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1233900</v>
+        <v>1755882</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>1233900</v>
+        <v>1755882</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>65712423</v>
+        <v>69152457</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>65712423</v>
+        <v>69152457</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1415621</v>
+        <v>1751382</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>1415621</v>
+        <v>1751382</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>615425</v>
+        <v>876520</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>615425</v>
+        <v>876520</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2212586</v>
+        <v>2631151</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>2212586</v>
+        <v>2631151</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>968543</v>
+        <v>1317538</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>968543</v>
+        <v>1317538</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>46035336</v>
+        <v>46243690</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>46035336</v>
+        <v>46243690</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>170144</v>
+        <v>170474</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>170144</v>
+        <v>170474</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2807292</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>2807292</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1873114</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>1873114</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>139296706</v>
+        <v>158508939</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>111568869</v>
+        <v>118454961</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>87628263</v>
+        <v>94707879</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>87628263</v>
+        <v>94707879</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>23940606</v>
+        <v>23747082</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>23940606</v>
+        <v>23747082</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>4659134</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>4659134</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1488565</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>1488565</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>929311</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>929311</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1114659</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>1114659</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>836229</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>836229</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>558028</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>558028</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>465719</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>465719</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>2587921</v>
+        <v>2599198</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>2587921</v>
+        <v>2599198</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1227020</v>
+        <v>1223932</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>1227020</v>
+        <v>1223932</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3157814</v>
+        <v>3182195</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>3157814</v>
+        <v>3182195</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>20516764</v>
+        <v>20584805</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>20516764</v>
+        <v>20584805</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>348510</v>
+        <v>2513086</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>348510</v>
+        <v>2513086</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1116828</v>
+        <v>1123049</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1116828</v>
+        <v>1123049</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1160148</v>
+        <v>1072153</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1160148</v>
+        <v>1072153</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>119515</v>
+        <v>120103</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>119515</v>
+        <v>120103</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>476393</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>476393</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>813912</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>813912</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>316778</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>316778</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>237497</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>237497</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>395977</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>395977</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1162761</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>1162761</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>211737</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>211737</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>159082</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>159082</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>265579</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>265579</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>186144</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>186144</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>133048</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>133048</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>106432</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>106432</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>79763</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>79763</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>50764640</v>
+        <v>51730736</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>55170727</v>
+        <v>55029016</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>465704</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>465704</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>132106</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>132106</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>209837</v>
+        <v>209178</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>209837</v>
+        <v>209178</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>50554803</v>
+        <v>51987262</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7092854</v>
+        <v>7072417</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>7092854</v>
+        <v>7072417</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>43461949</v>
+        <v>44914845</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>43461949</v>
+        <v>44914845</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>43461949</v>
+        <v>44914845</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>43461949</v>
+        <v>44914845</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>43461949</v>
+        <v>44914845</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
